--- a/artfynd/A 4120-2026 artfynd.xlsx
+++ b/artfynd/A 4120-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131228162</v>
       </c>
       <c r="B2" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131228149</v>
       </c>
       <c r="B3" t="n">
-        <v>57073</v>
+        <v>57075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4120-2026 artfynd.xlsx
+++ b/artfynd/A 4120-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131228162</v>
       </c>
       <c r="B2" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131228149</v>
       </c>
       <c r="B3" t="n">
-        <v>57075</v>
+        <v>57076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4120-2026 artfynd.xlsx
+++ b/artfynd/A 4120-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131228162</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131228149</v>
       </c>
       <c r="B3" t="n">
-        <v>57076</v>
+        <v>57079</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4120-2026 artfynd.xlsx
+++ b/artfynd/A 4120-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131228162</v>
       </c>
       <c r="B2" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131228149</v>
       </c>
       <c r="B3" t="n">
-        <v>57079</v>
+        <v>57080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4120-2026 artfynd.xlsx
+++ b/artfynd/A 4120-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131228162</v>
       </c>
       <c r="B2" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131228149</v>
       </c>
       <c r="B3" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4120-2026 artfynd.xlsx
+++ b/artfynd/A 4120-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131228162</v>
       </c>
       <c r="B2" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131228149</v>
       </c>
       <c r="B3" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 4120-2026 artfynd.xlsx
+++ b/artfynd/A 4120-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131228162</v>
+        <v>131228140</v>
       </c>
       <c r="B2" t="n">
-        <v>57087</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587136</v>
+        <v>587178</v>
       </c>
       <c r="R2" t="n">
-        <v>6419389</v>
+        <v>6419396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -783,7 +783,7 @@
         <v>131228149</v>
       </c>
       <c r="B3" t="n">
-        <v>57087</v>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,6 +882,111 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131228162</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>A 4120, Stengårdsnäs, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>587136</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6419389</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
